--- a/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
+++ b/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\Dropbox\EPS\Input Data for India 2.0\trans\SRPbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us\InputData\trans\SRPbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5D2952-C994-4A7A-A5D4-55036217A8F2}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26775" windowHeight="10710"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>SRPbVT Separately Regulated Pollutants by Vehicle Type</t>
   </si>
@@ -43,6 +42,12 @@
     <t>U.S. EPA</t>
   </si>
   <si>
+    <t>https://www.epa.gov/criteria-air-pollutants/naaqs-table</t>
+  </si>
+  <si>
+    <t>NAAQS Table</t>
+  </si>
+  <si>
     <t>Ships</t>
   </si>
   <si>
@@ -70,6 +75,12 @@
     <t>so we consider VOCs to be a separately-regulated pollutant whenever NOx/NO2 is separately-regulated.</t>
   </si>
   <si>
+    <t>VOCs</t>
+  </si>
+  <si>
+    <t>BC, OC</t>
+  </si>
+  <si>
     <t>As these are subsets of PM10 and sometimes PM2.5, we consider them to be separately-regulated whenever</t>
   </si>
   <si>
@@ -190,50 +201,14 @@
     <t>motorbikes</t>
   </si>
   <si>
-    <t>Boolean</t>
-  </si>
-  <si>
-    <t>We consider 2- and 3-wheelers together for India.</t>
-  </si>
-  <si>
-    <t>We use US values for rail, aircraft, and ships.</t>
-  </si>
-  <si>
-    <t>Automative Research Association of India (ARAI)</t>
-  </si>
-  <si>
-    <t>https://www.araiindia.com/pdf/Indian_Emission_Regulation_Booklet.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indian Emissions Regulations </t>
-  </si>
-  <si>
-    <t>Bharat Stage - VI norms - 2,3 wheelers (p1,17); LDVs (p29); HDVs (p47)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India's latest BS-VI emission standards are applicable for on-road vehicles. </t>
-  </si>
-  <si>
-    <t>CO2-</t>
-  </si>
-  <si>
-    <t>VOCs-</t>
-  </si>
-  <si>
-    <t>BC, OC-</t>
-  </si>
-  <si>
-    <t>Sox-</t>
-  </si>
-  <si>
-    <t>F-gases-</t>
+    <t>(Boolean)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +220,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -273,18 +256,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -562,19 +548,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="101.140625" customWidth="1"/>
+    <col min="2" max="2" width="101.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -582,395 +568,378 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B17" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="3">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="3">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="3">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B26" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
       <c r="B4">
         <v>0</v>
       </c>
@@ -1008,9 +977,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1028,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1049,9 +1018,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1069,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1090,9 +1059,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1113,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>

--- a/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
+++ b/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28221"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us\InputData\trans\SRPbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\Dropbox\EPS\Input Data for India 2.0\trans\SRPbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5D2952-C994-4A7A-A5D4-55036217A8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26775" windowHeight="10710"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="SRPbVT" sheetId="8" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>SRPbVT Separately Regulated Pollutants by Vehicle Type</t>
   </si>
@@ -36,49 +48,97 @@
     <t>On-Road Vehicles</t>
   </si>
   <si>
+    <t>Automative Research Association of India (ARAI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Emissions Regulations </t>
+  </si>
+  <si>
+    <t>https://www.araiindia.com/pdf/Indian_Emission_Regulation_Booklet.pdf</t>
+  </si>
+  <si>
+    <t>Bharat Stage - VI norms - 2,3 wheelers (p1,17); LDVs (p29); HDVs (p47)</t>
+  </si>
+  <si>
+    <t>Aircraft</t>
+  </si>
+  <si>
+    <t>U.S. EPA</t>
+  </si>
+  <si>
+    <t>undated (current as of 2018)</t>
+  </si>
+  <si>
+    <t>Regulations for Emissions from Aircraft</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/regulations-emissions-vehicles-and-engines/regulations-emissions-aircraft</t>
+  </si>
+  <si>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>U.S. EPA / Electronic Code of Federal Regulations</t>
+  </si>
+  <si>
+    <t>Regulations for Emissions from Locomotives</t>
+  </si>
+  <si>
+    <t>https://www.ecfr.gov/cgi-bin/text-idx?SID=159ba6f126272ea1995c71a43b7af309&amp;mc=true&amp;node=pt40.36.1033&amp;rgn=div5#se40.36.1033_1101</t>
+  </si>
+  <si>
+    <t>§1033.101 Exhaust emission standards, Table 1</t>
+  </si>
+  <si>
+    <t>Ships</t>
+  </si>
+  <si>
+    <t>EPA Finalizes More Stringent Standards for Control of Emissions from New Marine Compression-Ignition Engines at or Above 30 Liters per Cylinder</t>
+  </si>
+  <si>
+    <t>https://nepis.epa.gov/Exe/ZyPDF.cgi/P1005ZAD.PDF?Dockey=P1005ZAD.PDF</t>
+  </si>
+  <si>
+    <t>Page 3, the three paragraphs under the "New Clean Air Act Standards for Category 3 Engines" subheader</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>U.S. EPA</t>
-  </si>
-  <si>
-    <t>https://www.epa.gov/criteria-air-pollutants/naaqs-table</t>
-  </si>
-  <si>
-    <t>NAAQS Table</t>
-  </si>
-  <si>
-    <t>Ships</t>
-  </si>
-  <si>
-    <t>undated (current as of 2018)</t>
-  </si>
-  <si>
-    <t>Aircraft</t>
-  </si>
-  <si>
-    <t>https://www.epa.gov/regulations-emissions-vehicles-and-engines/regulations-emissions-aircraft</t>
-  </si>
-  <si>
-    <t>Regulations for Emissions from Aircraft</t>
-  </si>
-  <si>
-    <t>Rail</t>
-  </si>
-  <si>
-    <t>Regulations for Emissions from Locomotives</t>
+    <t>We consider 2- and 3-wheelers together for India.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India's latest BS-VI emission standards are applicable for on-road vehicles. </t>
+  </si>
+  <si>
+    <t>We use US values for rail, aircraft, and ships.</t>
+  </si>
+  <si>
+    <t>CO2-</t>
+  </si>
+  <si>
+    <t>CO2 is never considered a separately-regulated pollutant.  This variable's name refers to pollutants that are</t>
+  </si>
+  <si>
+    <t>regulated "separately" from CO2 (irrespective of whether a country uses CO2 or fuel economy standards).</t>
+  </si>
+  <si>
+    <t>VOCs-</t>
   </si>
   <si>
     <t>Although VOCs are not specifically named as a criteria pollutant, ozone is names, and ozone is formed from</t>
   </si>
   <si>
+    <t>the reaction of NOx/NO2 and VOCs in the atmosphere.  In practice, the emissions of NOx/NO2 + VOCs are regulated,</t>
+  </si>
+  <si>
     <t>so we consider VOCs to be a separately-regulated pollutant whenever NOx/NO2 is separately-regulated.</t>
   </si>
   <si>
-    <t>VOCs</t>
-  </si>
-  <si>
-    <t>BC, OC</t>
+    <t>Note that in some sources, VOCs are called HCs (hydrocarbons) or NMHCs (non-methane hydrocarbons).</t>
+  </si>
+  <si>
+    <t>BC, OC-</t>
   </si>
   <si>
     <t>As these are subsets of PM10 and sometimes PM2.5, we consider them to be separately-regulated whenever</t>
@@ -87,10 +147,43 @@
     <t>PM is separately-regulated.</t>
   </si>
   <si>
-    <t>CO2 is never considered a separately-regulated pollutant.  This variable's name refers to pollutants that are</t>
-  </si>
-  <si>
-    <t>regulated "separately" from CO2 (irrespective of whether a country uses CO2 or fuel economy standards).</t>
+    <t>Sox-</t>
+  </si>
+  <si>
+    <t>Where SOx is not regulated directly, it may still be regulated via the allowable sulfur content of diesel fuels.</t>
+  </si>
+  <si>
+    <t>For example, diesel fuel in the U.S. used by non-road modes must be ultra-low sulfur diesel (ULSD, below 15 ppm).</t>
+  </si>
+  <si>
+    <t>(See https://www.epa.gov/diesel-fuel-standards/diesel-fuel-standards-and-rulemakings )</t>
+  </si>
+  <si>
+    <t>However, a limit on sulfur in fuel correlates with the amount of fuel burned, so lacking other control technologies,</t>
+  </si>
+  <si>
+    <t>SOx emissions would scale with fuel use.  Thus, limits on sulfur in hydrocarbon fuels are not considered to be</t>
+  </si>
+  <si>
+    <t>"separate regulations" for purposes of this variable.</t>
+  </si>
+  <si>
+    <t>F-gases-</t>
+  </si>
+  <si>
+    <t>F-gases are handled in the industry sector, not the transportation sector (even if the emissions come from vehicle</t>
+  </si>
+  <si>
+    <t>air conditioning systems), so the setting in this variable does not have any effect.  We set it to zero, so that</t>
+  </si>
+  <si>
+    <t>if F-gas emissions are added to the transportation sector in the future, they will not be influenced by fuel</t>
+  </si>
+  <si>
+    <t>economy.</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
   <si>
     <t>CO2</t>
@@ -102,12 +195,18 @@
     <t>CO</t>
   </si>
   <si>
+    <t>NOx</t>
+  </si>
+  <si>
     <t>PM10</t>
   </si>
   <si>
     <t>PM2.5</t>
   </si>
   <si>
+    <t>SOx</t>
+  </si>
+  <si>
     <t>BC</t>
   </si>
   <si>
@@ -123,66 +222,6 @@
     <t>F-gases</t>
   </si>
   <si>
-    <t>F-gases are handled in the industry sector, not the transportation sector (even if the emissions come from vehicle</t>
-  </si>
-  <si>
-    <t>air conditioning systems), so the setting in this variable does not have any effect.  We set it to zero, so that</t>
-  </si>
-  <si>
-    <t>if F-gas emissions are added to the transportation sector in the future, they will not be influenced by fuel</t>
-  </si>
-  <si>
-    <t>economy.</t>
-  </si>
-  <si>
-    <t>NOx</t>
-  </si>
-  <si>
-    <t>SOx</t>
-  </si>
-  <si>
-    <t>the reaction of NOx/NO2 and VOCs in the atmosphere.  In practice, the emissions of NOx/NO2 + VOCs are regulated,</t>
-  </si>
-  <si>
-    <t>U.S. EPA / Electronic Code of Federal Regulations</t>
-  </si>
-  <si>
-    <t>Note that in some sources, VOCs are called HCs (hydrocarbons) or NMHCs (non-methane hydrocarbons).</t>
-  </si>
-  <si>
-    <t>§1033.101 Exhaust emission standards, Table 1</t>
-  </si>
-  <si>
-    <t>https://www.ecfr.gov/cgi-bin/text-idx?SID=159ba6f126272ea1995c71a43b7af309&amp;mc=true&amp;node=pt40.36.1033&amp;rgn=div5#se40.36.1033_1101</t>
-  </si>
-  <si>
-    <t>https://nepis.epa.gov/Exe/ZyPDF.cgi/P1005ZAD.PDF?Dockey=P1005ZAD.PDF</t>
-  </si>
-  <si>
-    <t>EPA Finalizes More Stringent Standards for Control of Emissions from New Marine Compression-Ignition Engines at or Above 30 Liters per Cylinder</t>
-  </si>
-  <si>
-    <t>Page 3, the three paragraphs under the "New Clean Air Act Standards for Category 3 Engines" subheader</t>
-  </si>
-  <si>
-    <t>However, a limit on sulfur in fuel correlates with the amount of fuel burned, so lacking other control technologies,</t>
-  </si>
-  <si>
-    <t>"separate regulations" for purposes of this variable.</t>
-  </si>
-  <si>
-    <t>Where SOx is not regulated directly, it may still be regulated via the allowable sulfur content of diesel fuels.</t>
-  </si>
-  <si>
-    <t>For example, diesel fuel in the U.S. used by non-road modes must be ultra-low sulfur diesel (ULSD, below 15 ppm).</t>
-  </si>
-  <si>
-    <t>(See https://www.epa.gov/diesel-fuel-standards/diesel-fuel-standards-and-rulemakings )</t>
-  </si>
-  <si>
-    <t>SOx emissions would scale with fuel use.  Thus, limits on sulfur in hydrocarbon fuels are not considered to be</t>
-  </si>
-  <si>
     <t>LDVs</t>
   </si>
   <si>
@@ -199,16 +238,13 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>(Boolean)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,14 +256,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -256,21 +284,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -548,19 +573,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="101.1328125" customWidth="1"/>
+    <col min="2" max="2" width="101.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -568,295 +593,312 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="3">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B9" s="2" t="s">
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B15" s="2" t="s">
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" s="3">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" s="3">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B17" s="3">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B24" s="3">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B26" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A53" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B26" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" t="s">
-        <v>29</v>
-      </c>
       <c r="L1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="M1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -877,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -895,9 +937,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -918,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -936,9 +978,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -977,9 +1019,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -997,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1018,9 +1060,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1038,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1059,9 +1101,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1082,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1103,4 +1145,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC51415-A991-447A-865F-DC6FF89B3DB4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C760013F-873C-432F-AAA8-2C4E4588024A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEBACB8-C04D-4672-82DC-BFAB3B4CD43C}"/>
 </file>